--- a/public/assets/excel_formats/sampleTemplate.xlsx
+++ b/public/assets/excel_formats/sampleTemplate.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajsr\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6140"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" forceFullCalc="1"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
     <t>Sr</t>
   </si>
@@ -27,29 +23,79 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
     <t>Column1</t>
   </si>
   <si>
+    <t>Free Text</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Column2</t>
+  </si>
+  <si>
+    <t>Dropdown</t>
+  </si>
+  <si>
+    <t>Value1|Value2|Value3</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Yes / No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,22 +110,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -126,7 +165,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -161,7 +200,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -369,50 +408,888 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E200"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" customWidth="1"/>
-    <col min="3" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="true" style="0"/>
+    <col min="2" max="2" width="22" customWidth="true" style="0"/>
+    <col min="3" max="3" width="22" customWidth="true" style="0"/>
+    <col min="4" max="4" width="22" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5"/>
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6"/>
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7"/>
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8"/>
+      <c r="E8"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9"/>
+      <c r="E9"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10"/>
+      <c r="E10"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11"/>
+      <c r="E11"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12"/>
+      <c r="E12"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13"/>
+      <c r="E13"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14"/>
+      <c r="E14"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15"/>
+      <c r="E15"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16"/>
+      <c r="E16"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="C17"/>
+      <c r="E17"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="C18"/>
+      <c r="E18"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="C19"/>
+      <c r="E19"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="C20"/>
+      <c r="E20"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="C21"/>
+      <c r="E21"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="C22"/>
+      <c r="E22"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="C23"/>
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="C24"/>
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="C25"/>
+      <c r="E25"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="C26"/>
+      <c r="E26"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="C27"/>
+      <c r="E27"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="C28"/>
+      <c r="E28"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="C29"/>
+      <c r="E29"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="C30"/>
+      <c r="E30"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="C31"/>
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="C32"/>
+      <c r="E32"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="C33"/>
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="C34"/>
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="C35"/>
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="C36"/>
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="C37"/>
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="C38"/>
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="C39"/>
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="C40"/>
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="C41"/>
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="C42"/>
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="C43"/>
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="C44"/>
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="C45"/>
+      <c r="E45"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="C46"/>
+      <c r="E46"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="C47"/>
+      <c r="E47"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="C48"/>
+      <c r="E48"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="C49"/>
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="C50"/>
+      <c r="E50"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="C51"/>
+      <c r="E51"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="C52"/>
+      <c r="E52"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="C53"/>
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="C54"/>
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="C55"/>
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="C56"/>
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="C57"/>
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="C58"/>
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="C59"/>
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="C60"/>
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="C61"/>
+      <c r="E61"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="C62"/>
+      <c r="E62"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="C63"/>
+      <c r="E63"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="C64"/>
+      <c r="E64"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="C65"/>
+      <c r="E65"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="C66"/>
+      <c r="E66"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="C67"/>
+      <c r="E67"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="C68"/>
+      <c r="E68"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="C69"/>
+      <c r="E69"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="C70"/>
+      <c r="E70"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="C71"/>
+      <c r="E71"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="C72"/>
+      <c r="E72"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="C73"/>
+      <c r="E73"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="C74"/>
+      <c r="E74"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="C75"/>
+      <c r="E75"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="C76"/>
+      <c r="E76"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="C77"/>
+      <c r="E77"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="C78"/>
+      <c r="E78"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="C79"/>
+      <c r="E79"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="C80"/>
+      <c r="E80"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="C81"/>
+      <c r="E81"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="C82"/>
+      <c r="E82"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="C83"/>
+      <c r="E83"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="C84"/>
+      <c r="E84"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="C85"/>
+      <c r="E85"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="C86"/>
+      <c r="E86"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="C87"/>
+      <c r="E87"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="C88"/>
+      <c r="E88"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="C89"/>
+      <c r="E89"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="C90"/>
+      <c r="E90"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="C91"/>
+      <c r="E91"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="C92"/>
+      <c r="E92"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="C93"/>
+      <c r="E93"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="C94"/>
+      <c r="E94"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="C95"/>
+      <c r="E95"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="C96"/>
+      <c r="E96"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="C97"/>
+      <c r="E97"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="C98"/>
+      <c r="E98"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="C99"/>
+      <c r="E99"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="C100"/>
+      <c r="E100"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="C101"/>
+      <c r="E101"/>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="C102"/>
+      <c r="E102"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="C103"/>
+      <c r="E103"/>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="C104"/>
+      <c r="E104"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="C105"/>
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="C106"/>
+      <c r="E106"/>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="C107"/>
+      <c r="E107"/>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="C108"/>
+      <c r="E108"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="C109"/>
+      <c r="E109"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="C110"/>
+      <c r="E110"/>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="C111"/>
+      <c r="E111"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="C112"/>
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="C113"/>
+      <c r="E113"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="C114"/>
+      <c r="E114"/>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="C115"/>
+      <c r="E115"/>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="C116"/>
+      <c r="E116"/>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="C117"/>
+      <c r="E117"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="C118"/>
+      <c r="E118"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="C119"/>
+      <c r="E119"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="C120"/>
+      <c r="E120"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="C121"/>
+      <c r="E121"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="C122"/>
+      <c r="E122"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="C123"/>
+      <c r="E123"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="C124"/>
+      <c r="E124"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="C125"/>
+      <c r="E125"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="C126"/>
+      <c r="E126"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="C127"/>
+      <c r="E127"/>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="C128"/>
+      <c r="E128"/>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="C129"/>
+      <c r="E129"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="C130"/>
+      <c r="E130"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="C131"/>
+      <c r="E131"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="C132"/>
+      <c r="E132"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="C133"/>
+      <c r="E133"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="C134"/>
+      <c r="E134"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="C135"/>
+      <c r="E135"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="C136"/>
+      <c r="E136"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="C137"/>
+      <c r="E137"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="C138"/>
+      <c r="E138"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="C139"/>
+      <c r="E139"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="C140"/>
+      <c r="E140"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="C141"/>
+      <c r="E141"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="C142"/>
+      <c r="E142"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="C143"/>
+      <c r="E143"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="C144"/>
+      <c r="E144"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="C145"/>
+      <c r="E145"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="C146"/>
+      <c r="E146"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="C147"/>
+      <c r="E147"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="C148"/>
+      <c r="E148"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="C149"/>
+      <c r="E149"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="C150"/>
+      <c r="E150"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="C151"/>
+      <c r="E151"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="C152"/>
+      <c r="E152"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="C153"/>
+      <c r="E153"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="C154"/>
+      <c r="E154"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="C155"/>
+      <c r="E155"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="C156"/>
+      <c r="E156"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="C157"/>
+      <c r="E157"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="C158"/>
+      <c r="E158"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="C159"/>
+      <c r="E159"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="C160"/>
+      <c r="E160"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="C161"/>
+      <c r="E161"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="C162"/>
+      <c r="E162"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="C163"/>
+      <c r="E163"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="C164"/>
+      <c r="E164"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="C165"/>
+      <c r="E165"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="C166"/>
+      <c r="E166"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="C167"/>
+      <c r="E167"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="C168"/>
+      <c r="E168"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="C169"/>
+      <c r="E169"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="C170"/>
+      <c r="E170"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="C171"/>
+      <c r="E171"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="C172"/>
+      <c r="E172"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="C173"/>
+      <c r="E173"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="C174"/>
+      <c r="E174"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="C175"/>
+      <c r="E175"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="C176"/>
+      <c r="E176"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="C177"/>
+      <c r="E177"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="C178"/>
+      <c r="E178"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="C179"/>
+      <c r="E179"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="C180"/>
+      <c r="E180"/>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="C181"/>
+      <c r="E181"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="C182"/>
+      <c r="E182"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="C183"/>
+      <c r="E183"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="C184"/>
+      <c r="E184"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="C185"/>
+      <c r="E185"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="C186"/>
+      <c r="E186"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="C187"/>
+      <c r="E187"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="C188"/>
+      <c r="E188"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="C189"/>
+      <c r="E189"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="C190"/>
+      <c r="E190"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="C191"/>
+      <c r="E191"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="C192"/>
+      <c r="E192"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="C193"/>
+      <c r="E193"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="C194"/>
+      <c r="E194"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="C195"/>
+      <c r="E195"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="C196"/>
+      <c r="E196"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="C197"/>
+      <c r="E197"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="C198"/>
+      <c r="E198"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="C199"/>
+      <c r="E199"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="C200"/>
+      <c r="E200"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C2:C200">
+      <formula1>"Free Text,Dropdown,Yes / No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E2:E200">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/public/assets/excel_formats/sampleTemplate.xlsx
+++ b/public/assets/excel_formats/sampleTemplate.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>Sr</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>Yes / No</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Column4</t>
   </si>
 </sst>
 </file>
@@ -487,8 +493,18 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="C5"/>
-      <c r="E5"/>
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6"/>
@@ -1272,8 +1288,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C2:C200">
-      <formula1>"Free Text,Dropdown,Yes / No"</formula1>
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" promptTitle="Type" prompt="File: each cell of this column holds one file name (e.g. abc.pdf) or one link." sqref="C2:C200">
+      <formula1>"Free Text,Dropdown,Yes / No,File"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E2:E200">
       <formula1>"Yes,No"</formula1>
